--- a/docentes/Aurioles Maldonado Luis Gustavo - Estadisticos 20212.xlsx
+++ b/docentes/Aurioles Maldonado Luis Gustavo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -851,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -881,6 +899,52 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920039</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Aurioles Maldonado Luis Gustavo - Estadisticos 20212.xlsx
+++ b/docentes/Aurioles Maldonado Luis Gustavo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,24 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -495,19 +477,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,19 +503,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -547,19 +529,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -573,19 +555,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -638,16 +620,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -661,16 +646,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -684,16 +672,19 @@
         <v>38</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>38</v>
       </c>
-      <c r="E4">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -707,16 +698,19 @@
         <v>31</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -769,16 +763,16 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9.5</v>
@@ -795,19 +789,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,19 +815,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,19 +841,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -899,52 +893,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920039</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Aurioles Maldonado Luis Gustavo - Estadisticos 20212.xlsx
+++ b/docentes/Aurioles Maldonado Luis Gustavo - Estadisticos 20212.xlsx
@@ -827,7 +827,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -853,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
